--- a/artfynd/A 56152-2025 artfynd.xlsx
+++ b/artfynd/A 56152-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021074</v>
+        <v>130021396</v>
       </c>
       <c r="B2" t="n">
         <v>57740</v>
@@ -704,24 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463102</v>
+        <v>463184</v>
       </c>
       <c r="R2" t="n">
-        <v>7041718</v>
+        <v>7041598</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,51 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130021083</v>
+        <v>130021074</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,26 +788,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463194</v>
+        <v>463102</v>
       </c>
       <c r="R3" t="n">
-        <v>7041747</v>
+        <v>7041718</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,19 +858,23 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -913,12 +889,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130021396</v>
+        <v>130021083</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,34 +923,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463184</v>
+        <v>463194</v>
       </c>
       <c r="R4" t="n">
-        <v>7041598</v>
+        <v>7041747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,29 +988,50 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2558,41 +2558,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130021410</v>
+        <v>130021077</v>
       </c>
       <c r="B19" t="n">
-        <v>91625</v>
+        <v>97668</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463239</v>
+        <v>463145</v>
       </c>
       <c r="R19" t="n">
-        <v>7041515</v>
+        <v>7041732</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,56 +2641,61 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130021077</v>
+        <v>130021087</v>
       </c>
       <c r="B20" t="n">
-        <v>97668</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2690,10 +2703,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463145</v>
+        <v>463238</v>
       </c>
       <c r="R20" t="n">
-        <v>7041732</v>
+        <v>7041799</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,6 +2741,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2741,6 +2759,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2758,10 +2796,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130021087</v>
+        <v>130021410</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>91625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,37 +2807,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463238</v>
+        <v>463239</v>
       </c>
       <c r="R21" t="n">
-        <v>7041799</v>
+        <v>7041515</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,55 +2865,24 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130021394</v>
+        <v>130021081</v>
       </c>
       <c r="B30" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,34 +3749,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463192</v>
+        <v>463097</v>
       </c>
       <c r="R30" t="n">
-        <v>7041600</v>
+        <v>7041741</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,36 +3814,57 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130021405</v>
+        <v>130021394</v>
       </c>
       <c r="B31" t="n">
         <v>57740</v>
@@ -3875,10 +3899,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463374</v>
+        <v>463192</v>
       </c>
       <c r="R31" t="n">
-        <v>7041740</v>
+        <v>7041600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3942,10 +3966,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130021081</v>
+        <v>130021405</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3953,37 +3977,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463097</v>
+        <v>463374</v>
       </c>
       <c r="R32" t="n">
-        <v>7041741</v>
+        <v>7041740</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4018,50 +4039,29 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 56152-2025 artfynd.xlsx
+++ b/artfynd/A 56152-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021396</v>
+        <v>130021074</v>
       </c>
       <c r="B2" t="n">
         <v>57740</v>
@@ -704,16 +704,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463184</v>
+        <v>463102</v>
       </c>
       <c r="R2" t="n">
-        <v>7041598</v>
+        <v>7041718</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,23 +769,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130021074</v>
+        <v>130021396</v>
       </c>
       <c r="B3" t="n">
         <v>57740</v>
@@ -806,24 +839,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463102</v>
+        <v>463184</v>
       </c>
       <c r="R3" t="n">
-        <v>7041718</v>
+        <v>7041598</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,41 +896,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -915,7 +915,7 @@
         <v>130021083</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130021080</v>
+        <v>130021407</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,37 +1049,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463122</v>
+        <v>463294</v>
       </c>
       <c r="R5" t="n">
-        <v>7041782</v>
+        <v>7041644</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,54 +1117,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130021407</v>
+        <v>130021080</v>
       </c>
       <c r="B6" t="n">
-        <v>91601</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,34 +1146,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463294</v>
+        <v>463122</v>
       </c>
       <c r="R6" t="n">
-        <v>7041644</v>
+        <v>7041782</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,18 +1217,44 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1264,7 +1264,7 @@
         <v>130021086</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>130021412</v>
       </c>
       <c r="B9" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>130021414</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>130021408</v>
       </c>
       <c r="B11" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130021400</v>
+        <v>130021404</v>
       </c>
       <c r="B13" t="n">
         <v>57740</v>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463187</v>
+        <v>463344</v>
       </c>
       <c r="R13" t="n">
-        <v>7041519</v>
+        <v>7041755</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130021404</v>
+        <v>130021400</v>
       </c>
       <c r="B14" t="n">
         <v>57740</v>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463344</v>
+        <v>463187</v>
       </c>
       <c r="R14" t="n">
-        <v>7041755</v>
+        <v>7041519</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2124,7 @@
         <v>130021084</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2558,49 +2558,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130021077</v>
+        <v>130021410</v>
       </c>
       <c r="B19" t="n">
-        <v>97668</v>
+        <v>91626</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463145</v>
+        <v>463239</v>
       </c>
       <c r="R19" t="n">
-        <v>7041732</v>
+        <v>7041515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2641,61 +2633,56 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130021087</v>
+        <v>130021077</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>97669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2703,10 +2690,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463238</v>
+        <v>463145</v>
       </c>
       <c r="R20" t="n">
-        <v>7041799</v>
+        <v>7041732</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2741,11 +2728,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2759,26 +2741,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2796,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130021410</v>
+        <v>130021087</v>
       </c>
       <c r="B21" t="n">
-        <v>91625</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,30 +2769,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463239</v>
+        <v>463238</v>
       </c>
       <c r="R21" t="n">
-        <v>7041515</v>
+        <v>7041799</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2865,24 +2834,55 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130021391</v>
+        <v>130021401</v>
       </c>
       <c r="B23" t="n">
         <v>57740</v>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463049</v>
+        <v>463196</v>
       </c>
       <c r="R23" t="n">
-        <v>7041720</v>
+        <v>7041524</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3093,7 +3093,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130021401</v>
+        <v>130021391</v>
       </c>
       <c r="B24" t="n">
         <v>57740</v>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463196</v>
+        <v>463049</v>
       </c>
       <c r="R24" t="n">
-        <v>7041524</v>
+        <v>7041720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,7 +3333,7 @@
         <v>130021413</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>130021415</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>130021081</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>130021411</v>
       </c>
       <c r="B33" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>130021082</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>130021085</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>130021078</v>
       </c>
       <c r="B36" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>130021409</v>
       </c>
       <c r="B37" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 56152-2025 artfynd.xlsx
+++ b/artfynd/A 56152-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021074</v>
+        <v>130021083</v>
       </c>
       <c r="B2" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463102</v>
+        <v>463194</v>
       </c>
       <c r="R2" t="n">
-        <v>7041718</v>
+        <v>7041747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,23 +751,19 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -787,12 +778,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130021396</v>
+        <v>130021074</v>
       </c>
       <c r="B3" t="n">
         <v>57740</v>
@@ -839,16 +830,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463184</v>
+        <v>463102</v>
       </c>
       <c r="R3" t="n">
-        <v>7041598</v>
+        <v>7041718</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,26 +895,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130021083</v>
+        <v>130021396</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +947,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463194</v>
+        <v>463184</v>
       </c>
       <c r="R4" t="n">
-        <v>7041747</v>
+        <v>7041598</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,50 +1009,29 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130021075</v>
+        <v>130021412</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>91626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,42 +1403,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463139</v>
+        <v>463279</v>
       </c>
       <c r="R8" t="n">
-        <v>7041707</v>
+        <v>7041801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,11 +1461,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, glest spridda längs ca 7 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1486,51 +1469,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130021412</v>
+        <v>130021075</v>
       </c>
       <c r="B9" t="n">
-        <v>91626</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,30 +1496,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463279</v>
+        <v>463139</v>
       </c>
       <c r="R9" t="n">
-        <v>7041801</v>
+        <v>7041707</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,6 +1566,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, glest spridda längs ca 7 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1604,16 +1579,41 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130021415</v>
+        <v>130021390</v>
       </c>
       <c r="B28" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463200</v>
+        <v>463045</v>
       </c>
       <c r="R28" t="n">
-        <v>7041585</v>
+        <v>7041711</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3636,10 +3636,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130021390</v>
+        <v>130021415</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3647,21 +3647,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463045</v>
+        <v>463200</v>
       </c>
       <c r="R29" t="n">
-        <v>7041711</v>
+        <v>7041585</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4423,49 +4423,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130021078</v>
+        <v>130021409</v>
       </c>
       <c r="B36" t="n">
-        <v>97669</v>
+        <v>91626</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463220</v>
+        <v>463216</v>
       </c>
       <c r="R36" t="n">
-        <v>7041764</v>
+        <v>7041521</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4506,65 +4498,67 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130021409</v>
+        <v>130021078</v>
       </c>
       <c r="B37" t="n">
-        <v>91626</v>
+        <v>97669</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463216</v>
+        <v>463220</v>
       </c>
       <c r="R37" t="n">
-        <v>7041521</v>
+        <v>7041764</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4605,18 +4599,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 56152-2025 artfynd.xlsx
+++ b/artfynd/A 56152-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021083</v>
+        <v>130021074</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463194</v>
+        <v>463102</v>
       </c>
       <c r="R2" t="n">
-        <v>7041747</v>
+        <v>7041718</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +756,23 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -778,12 +787,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130021074</v>
+        <v>130021396</v>
       </c>
       <c r="B3" t="n">
         <v>57740</v>
@@ -830,24 +839,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463102</v>
+        <v>463184</v>
       </c>
       <c r="R3" t="n">
-        <v>7041718</v>
+        <v>7041598</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,51 +896,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130021396</v>
+        <v>130021083</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,34 +923,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463184</v>
+        <v>463194</v>
       </c>
       <c r="R4" t="n">
-        <v>7041598</v>
+        <v>7041747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,29 +988,50 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130021410</v>
+        <v>130021087</v>
       </c>
       <c r="B19" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,30 +2569,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463239</v>
+        <v>463238</v>
       </c>
       <c r="R19" t="n">
-        <v>7041515</v>
+        <v>7041799</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,73 +2634,96 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130021077</v>
+        <v>130021410</v>
       </c>
       <c r="B20" t="n">
-        <v>97669</v>
+        <v>91626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463145</v>
+        <v>463239</v>
       </c>
       <c r="R20" t="n">
-        <v>7041732</v>
+        <v>7041515</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,61 +2764,56 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130021087</v>
+        <v>130021077</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>97669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2796,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463238</v>
+        <v>463145</v>
       </c>
       <c r="R21" t="n">
-        <v>7041799</v>
+        <v>7041732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,11 +2859,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2852,26 +2872,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -4423,41 +4423,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130021409</v>
+        <v>130021078</v>
       </c>
       <c r="B36" t="n">
-        <v>91626</v>
+        <v>97669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463216</v>
+        <v>463220</v>
       </c>
       <c r="R36" t="n">
-        <v>7041521</v>
+        <v>7041764</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4498,67 +4506,65 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130021078</v>
+        <v>130021409</v>
       </c>
       <c r="B37" t="n">
-        <v>97669</v>
+        <v>91626</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463220</v>
+        <v>463216</v>
       </c>
       <c r="R37" t="n">
-        <v>7041764</v>
+        <v>7041521</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4599,24 +4605,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 56152-2025 artfynd.xlsx
+++ b/artfynd/A 56152-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021074</v>
+        <v>130021083</v>
       </c>
       <c r="B2" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463102</v>
+        <v>463194</v>
       </c>
       <c r="R2" t="n">
-        <v>7041718</v>
+        <v>7041747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,23 +751,19 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -787,12 +778,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -912,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130021083</v>
+        <v>130021074</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,26 +914,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463194</v>
+        <v>463102</v>
       </c>
       <c r="R4" t="n">
-        <v>7041747</v>
+        <v>7041718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,19 +984,23 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,7 +1041,7 @@
         <v>130021407</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>130021080</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>130021086</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>130021412</v>
       </c>
       <c r="B8" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130021414</v>
+        <v>130021408</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>91643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,23 +1631,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1655,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463264</v>
+        <v>463236</v>
       </c>
       <c r="R10" t="n">
-        <v>7041556</v>
+        <v>7041582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,11 +1687,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130021408</v>
+        <v>130021414</v>
       </c>
       <c r="B11" t="n">
-        <v>91626</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,19 +1724,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1753,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463236</v>
+        <v>463264</v>
       </c>
       <c r="R11" t="n">
-        <v>7041582</v>
+        <v>7041556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,6 +1784,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,7 +1917,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130021404</v>
+        <v>130021400</v>
       </c>
       <c r="B13" t="n">
         <v>57740</v>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463344</v>
+        <v>463187</v>
       </c>
       <c r="R13" t="n">
-        <v>7041755</v>
+        <v>7041519</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130021400</v>
+        <v>130021404</v>
       </c>
       <c r="B14" t="n">
         <v>57740</v>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463187</v>
+        <v>463344</v>
       </c>
       <c r="R14" t="n">
-        <v>7041519</v>
+        <v>7041755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130021084</v>
+        <v>130021402</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,37 +2132,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463194</v>
+        <v>463201</v>
       </c>
       <c r="R15" t="n">
-        <v>7041782</v>
+        <v>7041523</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,7 +2196,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,54 +2205,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130021402</v>
+        <v>130021084</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,34 +2234,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463201</v>
+        <v>463194</v>
       </c>
       <c r="R16" t="n">
-        <v>7041523</v>
+        <v>7041782</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,7 +2301,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,18 +2310,44 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2558,37 +2558,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130021087</v>
+        <v>130021077</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>97686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2596,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463238</v>
+        <v>463145</v>
       </c>
       <c r="R19" t="n">
-        <v>7041799</v>
+        <v>7041732</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2634,11 +2635,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2652,26 +2648,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2692,7 +2668,7 @@
         <v>130021410</v>
       </c>
       <c r="B20" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2782,38 +2758,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130021077</v>
+        <v>130021087</v>
       </c>
       <c r="B21" t="n">
-        <v>97669</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2821,10 +2796,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463145</v>
+        <v>463238</v>
       </c>
       <c r="R21" t="n">
-        <v>7041732</v>
+        <v>7041799</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2859,6 +2834,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2872,6 +2852,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3093,7 +3093,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130021391</v>
+        <v>130021076</v>
       </c>
       <c r="B24" t="n">
         <v>57740</v>
@@ -3122,16 +3122,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463049</v>
+        <v>463133</v>
       </c>
       <c r="R24" t="n">
-        <v>7041720</v>
+        <v>7041708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,7 +3176,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre och några på gränsen till färska, i hyfsat riklig mängd längs minst 6 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,23 +3187,48 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130021076</v>
+        <v>130021391</v>
       </c>
       <c r="B25" t="n">
         <v>57740</v>
@@ -3224,24 +3257,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463133</v>
+        <v>463049</v>
       </c>
       <c r="R25" t="n">
-        <v>7041708</v>
+        <v>7041720</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3278,7 +3303,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och några på gränsen till färska, i hyfsat riklig mängd längs minst 6 meter på en granstam.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3289,41 +3314,16 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
         <v>130021413</v>
       </c>
       <c r="B26" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>130021415</v>
       </c>
       <c r="B29" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>130021081</v>
       </c>
       <c r="B30" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130021394</v>
+        <v>130021405</v>
       </c>
       <c r="B31" t="n">
         <v>57740</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463192</v>
+        <v>463374</v>
       </c>
       <c r="R31" t="n">
-        <v>7041600</v>
+        <v>7041740</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130021405</v>
+        <v>130021394</v>
       </c>
       <c r="B32" t="n">
         <v>57740</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463374</v>
+        <v>463192</v>
       </c>
       <c r="R32" t="n">
-        <v>7041740</v>
+        <v>7041600</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
         <v>130021411</v>
       </c>
       <c r="B33" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4161,37 +4161,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130021082</v>
+        <v>130021078</v>
       </c>
       <c r="B34" t="n">
-        <v>79088</v>
+        <v>97686</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4199,10 +4200,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463145</v>
+        <v>463220</v>
       </c>
       <c r="R34" t="n">
-        <v>7041721</v>
+        <v>7041764</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,11 +4238,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4255,26 +4251,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4292,10 +4268,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130021085</v>
+        <v>130021082</v>
       </c>
       <c r="B35" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4330,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463175</v>
+        <v>463145</v>
       </c>
       <c r="R35" t="n">
-        <v>7041811</v>
+        <v>7041721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4370,7 +4346,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På en skadad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4423,38 +4399,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130021078</v>
+        <v>130021085</v>
       </c>
       <c r="B36" t="n">
-        <v>97669</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4462,10 +4437,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463220</v>
+        <v>463175</v>
       </c>
       <c r="R36" t="n">
-        <v>7041764</v>
+        <v>7041811</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4500,6 +4475,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På en skadad gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4513,6 +4493,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4533,7 +4533,7 @@
         <v>130021409</v>
       </c>
       <c r="B37" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 56152-2025 artfynd.xlsx
+++ b/artfynd/A 56152-2025 artfynd.xlsx
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130021412</v>
+        <v>130021075</v>
       </c>
       <c r="B8" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,30 +1403,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463279</v>
+        <v>463139</v>
       </c>
       <c r="R8" t="n">
-        <v>7041801</v>
+        <v>7041707</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,6 +1473,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, glest spridda längs ca 7 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1469,26 +1486,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130021075</v>
+        <v>130021412</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>91659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,42 +1538,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463139</v>
+        <v>463279</v>
       </c>
       <c r="R9" t="n">
-        <v>7041707</v>
+        <v>7041801</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,11 +1596,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, glest spridda längs ca 7 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1579,41 +1604,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130021393</v>
+        <v>130021414</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463281</v>
+        <v>463264</v>
       </c>
       <c r="R11" t="n">
-        <v>7041580</v>
+        <v>7041556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130021414</v>
+        <v>130021393</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,21 +1826,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463264</v>
+        <v>463281</v>
       </c>
       <c r="R12" t="n">
-        <v>7041556</v>
+        <v>7041580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ganska rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2121,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130021084</v>
+        <v>130021402</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,37 +2132,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463194</v>
+        <v>463201</v>
       </c>
       <c r="R15" t="n">
-        <v>7041782</v>
+        <v>7041523</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,7 +2196,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,54 +2205,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130021402</v>
+        <v>130021084</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,34 +2234,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463201</v>
+        <v>463194</v>
       </c>
       <c r="R16" t="n">
-        <v>7041523</v>
+        <v>7041782</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,7 +2301,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,18 +2310,44 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130021081</v>
+        <v>130021405</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,37 +3749,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463097</v>
+        <v>463374</v>
       </c>
       <c r="R30" t="n">
-        <v>7041741</v>
+        <v>7041740</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3814,57 +3811,36 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130021405</v>
+        <v>130021394</v>
       </c>
       <c r="B31" t="n">
         <v>57741</v>
@@ -3899,10 +3875,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463374</v>
+        <v>463192</v>
       </c>
       <c r="R31" t="n">
-        <v>7041740</v>
+        <v>7041600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3966,10 +3942,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130021394</v>
+        <v>130021081</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3977,34 +3953,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463192</v>
+        <v>463097</v>
       </c>
       <c r="R32" t="n">
-        <v>7041600</v>
+        <v>7041741</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4039,29 +4018,50 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130021082</v>
+        <v>130021409</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>91659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,37 +4172,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463145</v>
+        <v>463216</v>
       </c>
       <c r="R34" t="n">
-        <v>7041721</v>
+        <v>7041521</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,62 +4230,31 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130021085</v>
+        <v>130021082</v>
       </c>
       <c r="B35" t="n">
         <v>79095</v>
@@ -4330,10 +4292,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463175</v>
+        <v>463145</v>
       </c>
       <c r="R35" t="n">
-        <v>7041811</v>
+        <v>7041721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4370,7 +4332,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På en skadad gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4423,10 +4385,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130021409</v>
+        <v>130021085</v>
       </c>
       <c r="B36" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,30 +4396,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463216</v>
+        <v>463175</v>
       </c>
       <c r="R36" t="n">
-        <v>7041521</v>
+        <v>7041811</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4492,24 +4461,55 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På en skadad gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 56152-2025 artfynd.xlsx
+++ b/artfynd/A 56152-2025 artfynd.xlsx
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130021414</v>
+        <v>130021393</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463264</v>
+        <v>463281</v>
       </c>
       <c r="R11" t="n">
-        <v>7041556</v>
+        <v>7041580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ganska rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130021393</v>
+        <v>130021414</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,21 +1826,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463281</v>
+        <v>463264</v>
       </c>
       <c r="R12" t="n">
-        <v>7041580</v>
+        <v>7041556</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3738,10 +3738,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130021405</v>
+        <v>130021081</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,34 +3749,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463374</v>
+        <v>463097</v>
       </c>
       <c r="R30" t="n">
-        <v>7041740</v>
+        <v>7041741</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3811,36 +3814,57 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130021394</v>
+        <v>130021405</v>
       </c>
       <c r="B31" t="n">
         <v>57741</v>
@@ -3875,10 +3899,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463192</v>
+        <v>463374</v>
       </c>
       <c r="R31" t="n">
-        <v>7041600</v>
+        <v>7041740</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3942,10 +3966,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130021081</v>
+        <v>130021394</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3953,37 +3977,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463097</v>
+        <v>463192</v>
       </c>
       <c r="R32" t="n">
-        <v>7041741</v>
+        <v>7041600</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4018,50 +4039,29 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 56152-2025 artfynd.xlsx
+++ b/artfynd/A 56152-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130021074</v>
+        <v>130021396</v>
       </c>
       <c r="B3" t="n">
         <v>57741</v>
@@ -830,24 +830,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463102</v>
+        <v>463184</v>
       </c>
       <c r="R3" t="n">
-        <v>7041718</v>
+        <v>7041598</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,48 +887,23 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130021396</v>
+        <v>130021074</v>
       </c>
       <c r="B4" t="n">
         <v>57741</v>
@@ -965,16 +932,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463184</v>
+        <v>463102</v>
       </c>
       <c r="R4" t="n">
-        <v>7041598</v>
+        <v>7041718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +986,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,26 +997,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130021080</v>
+        <v>130021407</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>91637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,37 +1049,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463122</v>
+        <v>463294</v>
       </c>
       <c r="R5" t="n">
-        <v>7041782</v>
+        <v>7041644</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,54 +1117,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130021407</v>
+        <v>130021080</v>
       </c>
       <c r="B6" t="n">
-        <v>91635</v>
+        <v>79095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,34 +1146,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463294</v>
+        <v>463122</v>
       </c>
       <c r="R6" t="n">
-        <v>7041644</v>
+        <v>7041782</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,18 +1217,44 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130021075</v>
+        <v>130021412</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>91661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,42 +1403,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463139</v>
+        <v>463279</v>
       </c>
       <c r="R8" t="n">
-        <v>7041707</v>
+        <v>7041801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,11 +1461,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, glest spridda längs ca 7 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1486,51 +1469,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130021412</v>
+        <v>130021075</v>
       </c>
       <c r="B9" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,30 +1496,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463279</v>
+        <v>463139</v>
       </c>
       <c r="R9" t="n">
-        <v>7041801</v>
+        <v>7041707</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,6 +1566,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, glest spridda längs ca 7 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1604,16 +1579,41 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1623,7 +1623,7 @@
         <v>130021408</v>
       </c>
       <c r="B10" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130021393</v>
+        <v>130021414</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463281</v>
+        <v>463264</v>
       </c>
       <c r="R11" t="n">
-        <v>7041580</v>
+        <v>7041556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130021414</v>
+        <v>130021393</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,21 +1826,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463264</v>
+        <v>463281</v>
       </c>
       <c r="R12" t="n">
-        <v>7041556</v>
+        <v>7041580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ganska rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,7 +1917,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130021404</v>
+        <v>130021400</v>
       </c>
       <c r="B13" t="n">
         <v>57741</v>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463344</v>
+        <v>463187</v>
       </c>
       <c r="R13" t="n">
-        <v>7041755</v>
+        <v>7041519</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130021400</v>
+        <v>130021404</v>
       </c>
       <c r="B14" t="n">
         <v>57741</v>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463187</v>
+        <v>463344</v>
       </c>
       <c r="R14" t="n">
-        <v>7041519</v>
+        <v>7041755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130021402</v>
+        <v>130021084</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,34 +2132,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463201</v>
+        <v>463194</v>
       </c>
       <c r="R15" t="n">
-        <v>7041523</v>
+        <v>7041782</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,7 +2199,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,28 +2208,54 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130021084</v>
+        <v>130021402</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,37 +2263,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463194</v>
+        <v>463201</v>
       </c>
       <c r="R16" t="n">
-        <v>7041782</v>
+        <v>7041523</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,7 +2327,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,44 +2336,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2561,7 +2561,7 @@
         <v>130021410</v>
       </c>
       <c r="B19" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,38 +2651,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130021077</v>
+        <v>130021087</v>
       </c>
       <c r="B20" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2690,10 +2689,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463145</v>
+        <v>463238</v>
       </c>
       <c r="R20" t="n">
-        <v>7041732</v>
+        <v>7041799</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2728,6 +2727,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2741,6 +2745,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2758,37 +2782,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130021087</v>
+        <v>130021077</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>97704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2796,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463238</v>
+        <v>463145</v>
       </c>
       <c r="R21" t="n">
-        <v>7041799</v>
+        <v>7041732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2834,11 +2859,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2852,26 +2872,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130021401</v>
+        <v>130021391</v>
       </c>
       <c r="B23" t="n">
         <v>57741</v>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463196</v>
+        <v>463049</v>
       </c>
       <c r="R23" t="n">
-        <v>7041524</v>
+        <v>7041720</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3093,7 +3093,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130021391</v>
+        <v>130021076</v>
       </c>
       <c r="B24" t="n">
         <v>57741</v>
@@ -3122,16 +3122,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463049</v>
+        <v>463133</v>
       </c>
       <c r="R24" t="n">
-        <v>7041720</v>
+        <v>7041708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,7 +3176,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre och några på gränsen till färska, i hyfsat riklig mängd längs minst 6 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,23 +3187,48 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130021076</v>
+        <v>130021401</v>
       </c>
       <c r="B25" t="n">
         <v>57741</v>
@@ -3224,24 +3257,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463133</v>
+        <v>463196</v>
       </c>
       <c r="R25" t="n">
-        <v>7041708</v>
+        <v>7041524</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3278,7 +3303,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och några på gränsen till färska, i hyfsat riklig mängd längs minst 6 meter på en granstam.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3289,41 +3314,16 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130021390</v>
+        <v>130021415</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463045</v>
+        <v>463200</v>
       </c>
       <c r="R28" t="n">
-        <v>7041711</v>
+        <v>7041585</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3636,10 +3636,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130021415</v>
+        <v>130021390</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3647,21 +3647,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463200</v>
+        <v>463045</v>
       </c>
       <c r="R29" t="n">
-        <v>7041585</v>
+        <v>7041711</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,7 +4071,7 @@
         <v>130021411</v>
       </c>
       <c r="B33" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130021409</v>
+        <v>130021082</v>
       </c>
       <c r="B34" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,30 +4172,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463216</v>
+        <v>463145</v>
       </c>
       <c r="R34" t="n">
-        <v>7041521</v>
+        <v>7041721</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4230,31 +4237,62 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130021082</v>
+        <v>130021085</v>
       </c>
       <c r="B35" t="n">
         <v>79095</v>
@@ -4292,10 +4330,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463145</v>
+        <v>463175</v>
       </c>
       <c r="R35" t="n">
-        <v>7041721</v>
+        <v>7041811</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4332,7 +4370,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På en skadad gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4385,37 +4423,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130021085</v>
+        <v>130021078</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>97704</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4423,10 +4462,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463175</v>
+        <v>463220</v>
       </c>
       <c r="R36" t="n">
-        <v>7041811</v>
+        <v>7041764</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4461,11 +4500,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På en skadad gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4479,26 +4513,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4516,49 +4530,41 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130021078</v>
+        <v>130021409</v>
       </c>
       <c r="B37" t="n">
-        <v>97702</v>
+        <v>91661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463220</v>
+        <v>463216</v>
       </c>
       <c r="R37" t="n">
-        <v>7041764</v>
+        <v>7041521</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4599,24 +4605,18 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 56152-2025 artfynd.xlsx
+++ b/artfynd/A 56152-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021083</v>
+        <v>130021396</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463194</v>
+        <v>463184</v>
       </c>
       <c r="R2" t="n">
-        <v>7041747</v>
+        <v>7041598</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,60 +748,39 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130021396</v>
+        <v>130021083</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,34 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463184</v>
+        <v>463194</v>
       </c>
       <c r="R3" t="n">
-        <v>7041598</v>
+        <v>7041747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,29 +853,50 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -906,7 +906,7 @@
         <v>130021074</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130021407</v>
+        <v>130021080</v>
       </c>
       <c r="B5" t="n">
-        <v>91637</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,34 +1049,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463294</v>
+        <v>463122</v>
       </c>
       <c r="R5" t="n">
-        <v>7041644</v>
+        <v>7041782</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,28 +1120,54 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130021080</v>
+        <v>130021407</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>91724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,37 +1175,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463122</v>
+        <v>463294</v>
       </c>
       <c r="R6" t="n">
-        <v>7041782</v>
+        <v>7041644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,44 +1243,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1264,7 +1264,7 @@
         <v>130021086</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>130021412</v>
       </c>
       <c r="B8" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>130021075</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130021408</v>
+        <v>130021393</v>
       </c>
       <c r="B10" t="n">
-        <v>91661</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,19 +1631,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1651,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463236</v>
+        <v>463281</v>
       </c>
       <c r="R10" t="n">
-        <v>7041582</v>
+        <v>7041580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,6 +1691,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,7 +1725,7 @@
         <v>130021414</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130021393</v>
+        <v>130021408</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>91748</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,23 +1835,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1850,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463281</v>
+        <v>463236</v>
       </c>
       <c r="R12" t="n">
-        <v>7041580</v>
+        <v>7041582</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,11 +1891,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130021400</v>
+        <v>130021404</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463187</v>
+        <v>463344</v>
       </c>
       <c r="R13" t="n">
-        <v>7041519</v>
+        <v>7041755</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130021404</v>
+        <v>130021400</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463344</v>
+        <v>463187</v>
       </c>
       <c r="R14" t="n">
-        <v>7041755</v>
+        <v>7041519</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130021084</v>
+        <v>130021402</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,37 +2132,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463194</v>
+        <v>463201</v>
       </c>
       <c r="R15" t="n">
-        <v>7041782</v>
+        <v>7041523</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,7 +2196,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,54 +2205,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130021402</v>
+        <v>130021084</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,34 +2234,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463201</v>
+        <v>463194</v>
       </c>
       <c r="R16" t="n">
-        <v>7041523</v>
+        <v>7041782</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,7 +2301,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,18 +2310,44 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2357,7 +2357,7 @@
         <v>130021392</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>130021395</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130021410</v>
+        <v>130021087</v>
       </c>
       <c r="B19" t="n">
-        <v>91661</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,30 +2569,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463239</v>
+        <v>463238</v>
       </c>
       <c r="R19" t="n">
-        <v>7041515</v>
+        <v>7041799</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,61 +2634,93 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130021087</v>
+        <v>130021077</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2689,10 +2728,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463238</v>
+        <v>463145</v>
       </c>
       <c r="R20" t="n">
-        <v>7041799</v>
+        <v>7041732</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,11 +2766,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2745,26 +2779,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2782,49 +2796,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130021077</v>
+        <v>130021410</v>
       </c>
       <c r="B21" t="n">
-        <v>97704</v>
+        <v>91748</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463145</v>
+        <v>463239</v>
       </c>
       <c r="R21" t="n">
-        <v>7041732</v>
+        <v>7041515</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2865,24 +2871,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
         <v>130021399</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130021391</v>
+        <v>130021401</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463049</v>
+        <v>463196</v>
       </c>
       <c r="R23" t="n">
-        <v>7041720</v>
+        <v>7041524</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3093,10 +3093,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130021076</v>
+        <v>130021391</v>
       </c>
       <c r="B24" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,24 +3122,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463133</v>
+        <v>463049</v>
       </c>
       <c r="R24" t="n">
-        <v>7041708</v>
+        <v>7041720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3176,7 +3168,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och några på gränsen till färska, i hyfsat riklig mängd längs minst 6 meter på en granstam.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3187,51 +3179,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130021401</v>
+        <v>130021076</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3257,16 +3224,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sjöarbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463196</v>
+        <v>463133</v>
       </c>
       <c r="R25" t="n">
-        <v>7041524</v>
+        <v>7041708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3303,7 +3278,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre och några på gränsen till färska, i hyfsat riklig mängd längs minst 6 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3314,26 +3289,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130021413</v>
+        <v>130021403</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>463054</v>
+        <v>463229</v>
       </c>
       <c r="R26" t="n">
-        <v>7041724</v>
+        <v>7041515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ganska rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3432,10 +3432,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130021403</v>
+        <v>130021413</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3443,21 +3443,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463229</v>
+        <v>463054</v>
       </c>
       <c r="R27" t="n">
-        <v>7041515</v>
+        <v>7041724</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130021415</v>
+        <v>130021390</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3545,21 +3545,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463200</v>
+        <v>463045</v>
       </c>
       <c r="R28" t="n">
-        <v>7041585</v>
+        <v>7041711</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3636,10 +3636,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130021390</v>
+        <v>130021415</v>
       </c>
       <c r="B29" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3647,21 +3647,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463045</v>
+        <v>463200</v>
       </c>
       <c r="R29" t="n">
-        <v>7041711</v>
+        <v>7041585</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3741,7 +3741,7 @@
         <v>130021081</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>130021405</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>130021394</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>130021411</v>
       </c>
       <c r="B33" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>130021082</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,37 +4292,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130021085</v>
+        <v>130021078</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4330,10 +4331,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463175</v>
+        <v>463220</v>
       </c>
       <c r="R35" t="n">
-        <v>7041811</v>
+        <v>7041764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4368,11 +4369,6 @@
           <t>2025-12-07</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På en skadad gran.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4386,26 +4382,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4423,38 +4399,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130021078</v>
+        <v>130021085</v>
       </c>
       <c r="B36" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4462,10 +4437,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463220</v>
+        <v>463175</v>
       </c>
       <c r="R36" t="n">
-        <v>7041764</v>
+        <v>7041811</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4500,6 +4475,11 @@
           <t>2025-12-07</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På en skadad gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4513,6 +4493,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4533,7 +4533,7 @@
         <v>130021409</v>
       </c>
       <c r="B37" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
